--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/AgentPrdInfo.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/AgentPrdInfo.xlsx
@@ -14,20 +14,17 @@
   <sheets>
     <sheet name="委托销售产品编码导入" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525" concurrentCalc="0"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>发行机构代码</t>
   </si>
   <si>
     <t>代理销售机构代码</t>
-  </si>
-  <si>
-    <t>备注</t>
   </si>
   <si>
     <t>产品登记编码</t>
@@ -427,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="27.5" style="1" customWidth="1"/>
@@ -435,7 +432,7 @@
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -443,16 +440,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B3" s="2"/>
     </row>
   </sheetData>
